--- a/event_registration_forms/013_donor_impact_showcase_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/013_donor_impact_showcase_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Details</t>
+          <t>Event Details (2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -894,63 +894,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2003,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2003, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3001,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3001, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3002,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3002, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3003,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3003, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
